--- a/artfynd/A 26460-2023 artfynd.xlsx
+++ b/artfynd/A 26460-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26460-2023 artfynd.xlsx
+++ b/artfynd/A 26460-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69562459</v>
+        <v>74962949</v>
       </c>
       <c r="B2" t="n">
-        <v>88937</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256756</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691708.0413166946</v>
+        <v>691730</v>
       </c>
       <c r="R2" t="n">
-        <v>6656986.908806339</v>
+        <v>6656971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 ex. i mossvegetation under gran.  Fruktkropp tätt förgrenad, hudfärgad. Toppar spetsiga med rödlila ton. Sporer fint vårtiga, 9-12 x 5-6 μm. Hyfer utan söljor.</t>
+          <t>10 kapslar på murken granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,9 +771,14 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Murken granlåga. # Gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,47 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74822129</v>
+        <v>56185536</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691739.9386595299</v>
+        <v>691905</v>
       </c>
       <c r="R3" t="n">
-        <v>6656981.554309273</v>
+        <v>6657403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,27 +870,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2006-12-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2006-12-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0,5 dm2 på stammen av levande asp, omkr. 118 cm. Känd sedan tidigare, se Gillis A. 5/10-01.</t>
+          <t>Ca. 10 ex. på murken asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +899,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Murken asplåga. # Asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,37 +917,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74822170</v>
+        <v>74822193</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -985,16 +955,21 @@
           <t>dm²</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691739.9386595299</v>
+        <v>691876</v>
       </c>
       <c r="R4" t="n">
-        <v>6656981.554309273</v>
+        <v>6657273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,24 +999,14 @@
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 dm2 på stammen av levande asp, omkr. 115 cm.</t>
+          <t>1 dm2 på stammen av levande asp, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,47 +1043,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74822145</v>
+        <v>74822195</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1127,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691745.2300364105</v>
+        <v>691866</v>
       </c>
       <c r="R5" t="n">
-        <v>6656976.31827001</v>
+        <v>6657273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,27 +1122,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca. 6 dm2 på stammen av levande asp, omkr. 106 cm.</t>
+          <t>0,5 dm2 på stammen av levande asp, omkr. 107 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1214,59 +1169,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74962949</v>
+        <v>75073622</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>937</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691729.9476894039</v>
+        <v>691828</v>
       </c>
       <c r="R6" t="n">
-        <v>6656971.013491695</v>
+        <v>6657122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1296,24 +1237,14 @@
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>10 kapslar på murken granlåga.</t>
+          <t>På murken asplåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,14 +1256,19 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med inslag av lövträd.</t>
+        </is>
+      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Murken granlåga. # Gran</t>
+          <t>Murken asplåga. # Asp</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,15 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75085976</v>
+        <v>75074002</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,21 +1297,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691729.9476894039</v>
+        <v>691720</v>
       </c>
       <c r="R7" t="n">
-        <v>6656971.013491695</v>
+        <v>6656961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,24 +1354,14 @@
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Flera ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,16 +1376,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Granlåga. # Gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1482,15 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75098992</v>
+        <v>75073772</v>
       </c>
       <c r="B8" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,27 +1404,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1527,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691926.4674776192</v>
+        <v>691720</v>
       </c>
       <c r="R8" t="n">
-        <v>6657273.844582451</v>
+        <v>6656961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1560,24 +1470,14 @@
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål i björkhögstubbe med fnösktickor, omkr. 107 cm.</t>
+          <t>Ca. 5 ex. under gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,14 +1489,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Björk</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1607,22 +1502,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75192169</v>
+        <v>75073514</v>
       </c>
       <c r="B9" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>5321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691741.3754710273</v>
+        <v>691780</v>
       </c>
       <c r="R9" t="n">
-        <v>6656963.591593535</v>
+        <v>6656972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,27 +1574,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2002-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-10-05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 137 cm.</t>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,14 +1596,19 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med inslag av lövträd.</t>
+        </is>
+      </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asplåga. # Asp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1746,55 +1626,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75200946</v>
+        <v>75085976</v>
       </c>
       <c r="B10" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101728</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Österbyggeby S om Aspdalssjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691926.4733245122</v>
+        <v>691730</v>
       </c>
       <c r="R10" t="n">
-        <v>6657283.363953645</v>
+        <v>6656971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,24 +1694,14 @@
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2001-10-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Puppkamrar i asplåga, omkr. 90 cm.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,14 +1713,19 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Granlåga. # Gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1871,10 +1736,1789 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75085977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6656961</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Granlåga. # Gran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75085987</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691774</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6656969</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granlåga, omkr. 53 cm.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Granlåga. # Gran</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74822164</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691740</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6656982</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 dm2 på stammen av levande asp, omkr. 118 cm. Känd sedan tidigare, se Gillis A. 5/10-01.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>75096165</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4872</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691866</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6657273</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kläckhål i veden på asphögstubbe, omkr. 85 cm.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>75098992</v>
+      </c>
+      <c r="B15" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>691926</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6657274</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe med fnösktickor, omkr. 107 cm.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>75098993</v>
+      </c>
+      <c r="B16" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>691849</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6657063</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe med fnösktickor.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>75192057</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>691741</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6656964</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 138 cm. Känd sedan tidigare, se Gillis A. 13/8-02.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>75192166</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>691999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6657271</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 124 cm.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>75192167</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>691972</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6657253</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på gammal, levande gran, omkr. 117 cm.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>75192234</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>691916</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6657293</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 115 cm.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>74822122</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>691745</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6656976</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 6 dm2 på stammen av levande asp, omkr. 107 cm. Känd sedan tidigare, se Gillis A. 13/8-02.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>74822129</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>691740</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6656982</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2006-12-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>0,5 dm2 på stammen av levande asp, omkr. 118 cm. Känd sedan tidigare, se Gillis A. 5/10-01.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>74822151</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>691906</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6657283</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 dm2 på stammen av levande asp, omkr. 115 cm.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>74822154</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>691886</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6657253</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2001-10-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0,5 dm2 på stammen av levande asp, omkr. 134 cm.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>69562459</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Österbyggeby S om Aspdalssjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>691708</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6656987</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2002-08-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 ex. i mossvegetation under gran.  Fruktkropp tätt förgrenad, hudfärgad. Toppar spetsiga med rödlila ton. Sporer fint vårtiga, 9-12 x 5-6 μm. Hyfer utan söljor.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
